--- a/合并产品信息表修改后.xlsx
+++ b/合并产品信息表修改后.xlsx
@@ -7,9 +7,9 @@
     <workbookView windowWidth="27945" windowHeight="12525" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="底价目录_20260112" sheetId="2" r:id="rId1"/>
-    <sheet name="明星产品_20260512" sheetId="3" r:id="rId2"/>
-    <sheet name="产品信息_华英" sheetId="4" r:id="rId3"/>
+    <sheet name="底价目录_20260112" sheetId="1" r:id="rId1"/>
+    <sheet name="明星产品_20260512" sheetId="2" r:id="rId2"/>
+    <sheet name="产品信息_华英" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="421">
   <si>
     <t>序号</t>
   </si>
@@ -442,6 +442,20 @@
     <t>注射600公斤体重</t>
   </si>
   <si>
+    <t>畅健®</t>
+  </si>
+  <si>
+    <t>无抗高效广谱抑菌口服液</t>
+  </si>
+  <si>
+    <t>1、高效抑制大肠杆菌、沙门氏菌、鸭疫里默氏杆菌、巴氏杆菌、魏氏梭菌等动物致病菌。
+2、作为抗原活性物质，激活免疫系统，解除免疫抑制。
+3、平衡肠道有益菌群，利于动物生长，提高饲料利用率。</t>
+  </si>
+  <si>
+    <t>本品500ml/瓶兑水800斤，全天量集中饮用6-7小时，连用3-5天。</t>
+  </si>
+  <si>
     <t>气管栓塞呼吸道药</t>
   </si>
   <si>
@@ -634,6 +648,41 @@
   </si>
   <si>
     <t>注射250kg体重</t>
+  </si>
+  <si>
+    <t>超吉拍档（不用稀释液的超吉拍档）</t>
+  </si>
+  <si>
+    <t>防治细菌病、支原体和滑液囊支原体引起的心包炎、肝周炎、气囊炎、腹膜炎、关节炎、龙骨液化等症状。</t>
+  </si>
+  <si>
+    <t>7日龄和油苗混合：鸡，1瓶本品配合3瓶油苗；鸭，1瓶本品配合2瓶油苗（1瓶超吉拍档用40ml纯净水稀释后油苗混合注射即可）。
+平时和油苗配伍用于1000斤体重，治疗滑液囊支原体和细菌性疾病每瓶注射600斤体重。</t>
+  </si>
+  <si>
+    <t>抗体类产品</t>
+  </si>
+  <si>
+    <t>痛风抗体类产品</t>
+  </si>
+  <si>
+    <t>抚风®</t>
+  </si>
+  <si>
+    <t>6g/瓶×80瓶/箱</t>
+  </si>
+  <si>
+    <t>1、痛风抗体效价高达212.5以上，并复配高效免疫增强剂，真正实现水禽痛风的可防可控。
+2、更易联合用药，可与抗生素、水剂类抗体联合，有利于扩大防治范围，减少动物应激。
+3、冻干抗体，体积小，易运输、易保存，抗体效价更稳定
+用于预防水禽痛风，适用于各品种水禽的各个养殖阶段</t>
+  </si>
+  <si>
+    <t>1-3日龄，400羽/瓶；
+3-10日龄，200-250羽/瓶。</t>
+  </si>
+  <si>
+    <t>400只</t>
   </si>
   <si>
     <t>抗病毒类产品</t>
@@ -873,102 +922,19 @@
     <t>500ml/瓶兑水1000斤，全天量饮用5-7小时，连用4日。</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（中药）</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>利达美</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（第二天见效）250ml</t>
-    </r>
+    <t>（中药）利达美（第二天见效）250ml</t>
   </si>
   <si>
     <t>清瘟解毒口服液</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>流感病毒及风热</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>感冒</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>中后期以及其他原因引起采食量下降、大群精神尚可、高死亡率的治疗。剖检可见的肺出血、心肌出血、胰腺出血、肾脏条状出血、气囊浑浊等症状。</t>
-    </r>
+    <t>流感病毒及风热感冒中后期以及其他原因引起采食量下降、大群精神尚可、高死亡率的治疗。剖检可见的肺出血、心肌出血、胰腺出血、肾脏条状出血、气囊浑浊等症状。</t>
   </si>
   <si>
     <t>250ml/瓶兑水400斤，饮用6小时，连用4天。</t>
   </si>
   <si>
-    <r>
-      <t>（中药）</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>利达美</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（第二天见效）500ml</t>
-    </r>
+    <t>（中药）利达美（第二天见效）500ml</t>
   </si>
   <si>
     <t>500ml/瓶兑水800斤，饮用6小时，连用4天。</t>
@@ -1007,15 +973,23 @@
     <t>主要用于病毒性感冒和风热感冒引起高死亡率，肉髯发绀、发紫，采食量严重下降、精神差的治疗；剖检可见气管出血，肺脏淤血、出血、水肿，心肌出血、心包积液，肾脏出血等症状。</t>
   </si>
   <si>
-    <t>温炎消</t>
-  </si>
-  <si>
     <t>于各种原因引起的高烧不退、精神沉郁、眼睑发红、咳嗽、甩鼻、流鼻涕等症状的治疗。</t>
   </si>
   <si>
     <t>本品500ml兑水 2000斤，全天量集中7-8小时饮完，连用 4-5天（饮水不得低于1800斤水）</t>
   </si>
   <si>
+    <t>控孤TM</t>
+  </si>
+  <si>
+    <t>5g/瓶×80瓶/箱</t>
+  </si>
+  <si>
+    <t>1、效价高。精制浓缩抗体，防治水禽呼肠孤病毒病更有效。
+2、联合易。可与多种水剂类抗体联合使用，实现一针防多病。
+3、体积小。冻干剂型，易运输、保存，抗体效价更稳定。</t>
+  </si>
+  <si>
     <t>肠道类产品</t>
   </si>
   <si>
@@ -1028,6 +1002,42 @@
     <t>本品 500g/袋兑水 1000斤，全天量集中饮水 6小时，连用 4天。</t>
   </si>
   <si>
+    <t>预防水禽传染性浆膜炎</t>
+  </si>
+  <si>
+    <t>浆小白</t>
+  </si>
+  <si>
+    <t>250ml/瓶×40瓶/箱</t>
+  </si>
+  <si>
+    <t>1、用于预防水禽传染性浆膜炎。 
+2、调理肠道菌群平衡，提高机体抗病能力。
+3、优化筛选的嗜酸乳杆菌可高效分泌荚膜多糖类似物，刺激动物肠道分泌多种靶向鸭疫里默氏杆菌的黏膜免疫抗体（SIgA），有效预防水禽传染性浆膜炎的发生。
+4、嗜酸乳杆菌还可分泌乳酸菌素、嗜酸杆菌素等多种抑菌物质，对各种肠道致病菌产生拮抗作用，调理肠道菌群平衡，提高机体抗病能力。</t>
+  </si>
+  <si>
+    <t>本品250ml/瓶可用于2500只鸭、鹅，饮水使用4—6小时，也可拌料使用。</t>
+  </si>
+  <si>
+    <t>2500只</t>
+  </si>
+  <si>
+    <t>浆小白（清解合剂）</t>
+  </si>
+  <si>
+    <t>1、靶向益生菌发酵产生的荚膜多糖类似物刺激机体产生黏膜免疫抗体，起到预防鸭疫菌侵入机体的作用。
+2、中药清解合剂具有清热凉血功效，可有效预防包心包肝的发生。
+3、用于预防肉鸡、蛋鸡、种鸡的鸭疫里默氏杆菌感染。 
+4、调理肠道菌群平衡，提高机体抗病能力。</t>
+  </si>
+  <si>
+    <t>本品250ml/瓶可用于4000只鸡（种鸡、三黄鸡、麻鸡等大日龄家禽根据日龄情况可按6000kg体重/瓶），集中饮水使用4—6小时，也可拌料使用</t>
+  </si>
+  <si>
+    <t>4000只</t>
+  </si>
+  <si>
     <t>营养增料促生长</t>
   </si>
   <si>
@@ -1076,9 +1086,6 @@
     <t>腺胃炎产品</t>
   </si>
   <si>
-    <t>双胃康</t>
-  </si>
-  <si>
     <t>液态苍术木香粗提物（复配型）</t>
   </si>
   <si>
@@ -1097,7 +1104,7 @@
     <t>兑水800斤，饮用6-8小时，连用4-5天。</t>
   </si>
   <si>
-    <t>羡康100g</t>
+    <t>(中药)羡康100g</t>
   </si>
   <si>
     <t>天然植物饲料原料 干姜粗提物</t>
@@ -1110,7 +1117,7 @@
     <t>本品 100g兑水400斤，全天量集中饮用 8小时，连用 4-5天</t>
   </si>
   <si>
-    <t>羡康500g</t>
+    <t>(中药) 羡康500g</t>
   </si>
   <si>
     <t>本品 500g兑水2500斤，全天量集中饮用 8小时，连用 4-5天</t>
@@ -1203,74 +1210,13 @@
     <t>营养类</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（市面500g12-20元）</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>高免鱼肝油</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（蛋鸡用的多）箱</t>
-    </r>
+    <t>（市面500g12-20元）高免鱼肝油（蛋鸡用的多）箱</t>
   </si>
   <si>
     <t>200g/袋*50袋/箱</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1、提高</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>机体免疫力</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>，减少疾病发生，缓解疫苗接种后应激反应。2、防止维生素A、D、E，预防瘫痪脑软化症。3、增强机体免疫力，减少疾病发生。4、促进钙磷吸收，增强蛋壳硬度，改善蛋壳色泽，防治腿病，软骨症，脑软化症。</t>
-    </r>
+    <t>1、提高机体免疫力，减少疾病发生，缓解疫苗接种后应激反应。2、防止维生素A、D、E，预防瘫痪脑软化症。3、增强机体免疫力，减少疾病发生。4、促进钙磷吸收，增强蛋壳硬度，改善蛋壳色泽，防治腿病，软骨症，脑软化症。</t>
   </si>
   <si>
     <t>每袋200克，饮水4000斤（拌料2000斤），饮用8小时，连用3天。</t>
@@ -1279,37 +1225,7 @@
     <t>卖价5.5-6元</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（市面500g12-20元）</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>高免鱼肝油</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（蛋鸡用的多）桶</t>
-    </r>
+    <t>（市面500g12-20元）高免鱼肝油（蛋鸡用的多）桶</t>
   </si>
   <si>
     <t>200g/袋*60袋/桶</t>
@@ -1431,6 +1347,18 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2E2E2E"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -1576,30 +1504,19 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1788,7 +1705,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -1818,17 +1735,19 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
+      <top/>
+      <bottom style="thin">
         <color auto="1"/>
-      </top>
-      <bottom/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -1884,6 +1803,24 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1987,152 +1924,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="14">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="15">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="14">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="16">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2146,11 +2083,44 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2167,36 +2137,22 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2546,27 +2502,27 @@
   <dimension ref="A1:J30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="9" style="8"/>
+    <col min="1" max="1" width="9" style="19" customWidth="1"/>
     <col min="2" max="2" width="29.625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="13.125" style="19" customWidth="1"/>
     <col min="4" max="4" width="17.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9" style="1"/>
+    <col min="5" max="5" width="9" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.25" style="1" customWidth="1"/>
     <col min="7" max="7" width="18" style="1" customWidth="1"/>
-    <col min="8" max="8" width="7.125" style="8" customWidth="1"/>
+    <col min="8" max="8" width="7.125" style="19" customWidth="1"/>
     <col min="9" max="9" width="10.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.625" style="8"/>
-    <col min="11" max="14" width="12.625"/>
+    <col min="10" max="10" width="12.625" style="19" customWidth="1"/>
+    <col min="11" max="14" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:10">
-      <c r="A1" s="9" t="s">
+    <row r="1" ht="27" customHeight="1" spans="1:10">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -2581,24 +2537,24 @@
       <c r="G1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="20" t="s">
         <v>4</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="20" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="10">
+      <c r="A2" s="21">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="19">
+      <c r="C2" s="29">
         <v>0.2</v>
       </c>
       <c r="D2" s="3" t="s">
@@ -2614,25 +2570,25 @@
       <c r="G2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="21" t="s">
         <v>11</v>
       </c>
       <c r="I2" s="4">
         <f>5.3/0.88</f>
         <v>6.02272727272727</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="21" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="10">
+      <c r="A3" s="21">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="19">
+      <c r="C3" s="29">
         <v>0.5</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -2648,23 +2604,23 @@
       <c r="G3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="21" t="s">
         <v>15</v>
       </c>
       <c r="I3" s="4">
         <f>23.3/0.88</f>
         <v>26.4772727272727</v>
       </c>
-      <c r="J3" s="10"/>
+      <c r="J3" s="21"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="10">
+      <c r="A4" s="21">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="29">
         <v>0.5</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -2680,23 +2636,23 @@
       <c r="G4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="21" t="s">
         <v>11</v>
       </c>
       <c r="I4" s="4">
         <f>3.7/0.88</f>
         <v>4.20454545454546</v>
       </c>
-      <c r="J4" s="10"/>
+      <c r="J4" s="21"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="10">
+      <c r="A5" s="21">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="29">
         <v>0.3</v>
       </c>
       <c r="D5" s="3" t="s">
@@ -2712,25 +2668,25 @@
       <c r="G5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="21" t="s">
         <v>19</v>
       </c>
       <c r="I5" s="4">
         <f>8.6/0.88</f>
         <v>9.77272727272727</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="21" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="10">
+      <c r="A6" s="21">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="29" t="s">
         <v>21</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -2746,25 +2702,25 @@
       <c r="G6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="21" t="s">
         <v>15</v>
       </c>
       <c r="I6" s="4">
         <f>5.1/0.88</f>
         <v>5.79545454545454</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="21" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="10">
+      <c r="A7" s="21">
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="29" t="s">
         <v>21</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -2780,23 +2736,23 @@
       <c r="G7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="21" t="s">
         <v>15</v>
       </c>
       <c r="I7" s="4">
         <f>5.1/0.88</f>
         <v>5.79545454545454</v>
       </c>
-      <c r="J7" s="10"/>
+      <c r="J7" s="21"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="10">
+      <c r="A8" s="21">
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="29">
         <v>0.325</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -2812,25 +2768,25 @@
       <c r="G8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="21" t="s">
         <v>19</v>
       </c>
       <c r="I8" s="4">
         <f>6.9/0.88</f>
         <v>7.84090909090909</v>
       </c>
-      <c r="J8" s="10" t="s">
+      <c r="J8" s="21" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="10">
+      <c r="A9" s="21">
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="29" t="s">
         <v>27</v>
       </c>
       <c r="D9" s="3" t="s">
@@ -2852,18 +2808,18 @@
       <c r="I9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="J9" s="10" t="s">
+      <c r="J9" s="21" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="10">
+      <c r="A10" s="21">
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="29" t="s">
         <v>31</v>
       </c>
       <c r="D10" s="3" t="s">
@@ -2885,18 +2841,18 @@
       <c r="I10" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="J10" s="10" t="s">
+      <c r="J10" s="21" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="10">
+      <c r="A11" s="21">
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="29">
         <v>0.1</v>
       </c>
       <c r="D11" s="3" t="s">
@@ -2912,23 +2868,23 @@
       <c r="G11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="21" t="s">
         <v>35</v>
       </c>
       <c r="I11" s="4">
         <f>5.4/0.88</f>
         <v>6.13636363636364</v>
       </c>
-      <c r="J11" s="10"/>
+      <c r="J11" s="21"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="10">
+      <c r="A12" s="21">
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="29">
         <v>0.2</v>
       </c>
       <c r="D12" s="3" t="s">
@@ -2944,25 +2900,25 @@
       <c r="G12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="21" t="s">
         <v>11</v>
       </c>
       <c r="I12" s="4">
         <f>4.1/0.88</f>
         <v>4.65909090909091</v>
       </c>
-      <c r="J12" s="10" t="s">
+      <c r="J12" s="21" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="10">
+      <c r="A13" s="21">
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="29">
         <v>0.12</v>
       </c>
       <c r="D13" s="3" t="s">
@@ -2978,25 +2934,25 @@
       <c r="G13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="21" t="s">
         <v>11</v>
       </c>
       <c r="I13" s="4">
         <f>5.2/0.88</f>
         <v>5.90909090909091</v>
       </c>
-      <c r="J13" s="10" t="s">
+      <c r="J13" s="21" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="10">
+      <c r="A14" s="21">
         <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="29">
         <v>0.25</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -3012,25 +2968,25 @@
       <c r="G14" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H14" s="10" t="s">
+      <c r="H14" s="21" t="s">
         <v>42</v>
       </c>
       <c r="I14" s="4">
         <f>13.3/0.88</f>
         <v>15.1136363636364</v>
       </c>
-      <c r="J14" s="10" t="s">
+      <c r="J14" s="21" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="10">
+      <c r="A15" s="21">
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="19">
+      <c r="C15" s="29">
         <v>0.5</v>
       </c>
       <c r="D15" s="3" t="s">
@@ -3046,25 +3002,25 @@
       <c r="G15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H15" s="10" t="s">
+      <c r="H15" s="21" t="s">
         <v>44</v>
       </c>
       <c r="I15" s="4">
         <f>21.1/0.88</f>
         <v>23.9772727272727</v>
       </c>
-      <c r="J15" s="10" t="s">
+      <c r="J15" s="21" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="10">
+      <c r="A16" s="21">
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="19">
+      <c r="C16" s="29">
         <v>0.2</v>
       </c>
       <c r="D16" s="3" t="s">
@@ -3080,25 +3036,25 @@
       <c r="G16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H16" s="10" t="s">
+      <c r="H16" s="21" t="s">
         <v>44</v>
       </c>
       <c r="I16" s="4">
         <f>10.7/0.88</f>
         <v>12.1590909090909</v>
       </c>
-      <c r="J16" s="10" t="s">
+      <c r="J16" s="21" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" ht="27" spans="1:10">
-      <c r="A17" s="10">
+    <row r="17" ht="27" customHeight="1" spans="1:10">
+      <c r="A17" s="21">
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="29" t="s">
         <v>47</v>
       </c>
       <c r="D17" s="3" t="s">
@@ -3114,25 +3070,25 @@
       <c r="G17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H17" s="10" t="s">
+      <c r="H17" s="21" t="s">
         <v>11</v>
       </c>
       <c r="I17" s="4">
         <f>8.1/0.88</f>
         <v>9.20454545454545</v>
       </c>
-      <c r="J17" s="10" t="s">
+      <c r="J17" s="21" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="10">
+      <c r="A18" s="21">
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="29" t="s">
         <v>49</v>
       </c>
       <c r="D18" s="3" t="s">
@@ -3147,25 +3103,25 @@
       <c r="G18" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H18" s="10" t="s">
+      <c r="H18" s="21" t="s">
         <v>34</v>
       </c>
       <c r="I18" s="4">
         <f>27.2/0.88</f>
         <v>30.9090909090909</v>
       </c>
-      <c r="J18" s="10" t="s">
+      <c r="J18" s="21" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="19" ht="27" spans="1:10">
-      <c r="A19" s="10">
+    <row r="19" ht="27" customHeight="1" spans="1:10">
+      <c r="A19" s="21">
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="19">
+      <c r="C19" s="29">
         <v>0.3</v>
       </c>
       <c r="D19" s="3" t="s">
@@ -3180,25 +3136,25 @@
       <c r="G19" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H19" s="10" t="s">
+      <c r="H19" s="21" t="s">
         <v>52</v>
       </c>
       <c r="I19" s="4">
         <f>10.3/0.88</f>
         <v>11.7045454545455</v>
       </c>
-      <c r="J19" s="10" t="s">
+      <c r="J19" s="21" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="20" ht="27" spans="1:10">
-      <c r="A20" s="10">
+    <row r="20" ht="27" customHeight="1" spans="1:10">
+      <c r="A20" s="21">
         <v>18</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="29">
         <v>0.3</v>
       </c>
       <c r="D20" s="3" t="s">
@@ -3213,25 +3169,25 @@
       <c r="G20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H20" s="10" t="s">
+      <c r="H20" s="21" t="s">
         <v>52</v>
       </c>
       <c r="I20" s="4">
         <f>9/0.88</f>
         <v>10.2272727272727</v>
       </c>
-      <c r="J20" s="10" t="s">
+      <c r="J20" s="21" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="10">
+      <c r="A21" s="21">
         <v>19</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="19">
+      <c r="C21" s="29">
         <v>0.3</v>
       </c>
       <c r="D21" s="3" t="s">
@@ -3246,25 +3202,25 @@
       <c r="G21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H21" s="10" t="s">
+      <c r="H21" s="21" t="s">
         <v>55</v>
       </c>
       <c r="I21" s="4">
         <f>7.8/0.88</f>
         <v>8.86363636363636</v>
       </c>
-      <c r="J21" s="10" t="s">
+      <c r="J21" s="21" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="10">
+      <c r="A22" s="21">
         <v>20</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="19">
+      <c r="C22" s="29">
         <v>0.1</v>
       </c>
       <c r="D22" s="3" t="s">
@@ -3286,16 +3242,16 @@
       <c r="I22" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="J22" s="10"/>
+      <c r="J22" s="21"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="10">
+      <c r="A23" s="21">
         <v>21</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C23" s="19">
+      <c r="C23" s="29">
         <v>0.8</v>
       </c>
       <c r="D23" s="3" t="s">
@@ -3310,99 +3266,67 @@
       <c r="G23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H23" s="10" t="s">
+      <c r="H23" s="21" t="s">
         <v>58</v>
       </c>
       <c r="I23" s="4">
         <f>27.8/0.88</f>
         <v>31.5909090909091</v>
       </c>
-      <c r="J23" s="10" t="s">
+      <c r="J23" s="21" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="B24" s="20"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="21"/>
-      <c r="I24" s="21"/>
-      <c r="J24" s="21"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="25"/>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="21"/>
-      <c r="B25" s="20"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="21"/>
-      <c r="H25" s="21"/>
-      <c r="I25" s="21"/>
-      <c r="J25" s="21"/>
+      <c r="A25" s="31"/>
+      <c r="J25" s="32"/>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="21"/>
-      <c r="B26" s="20"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="21"/>
-      <c r="J26" s="21"/>
+      <c r="A26" s="31"/>
+      <c r="J26" s="32"/>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="21"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
-      <c r="I27" s="21"/>
-      <c r="J27" s="21"/>
+      <c r="A27" s="31"/>
+      <c r="J27" s="32"/>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="21"/>
-      <c r="B28" s="20"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="21"/>
+      <c r="A28" s="31"/>
+      <c r="J28" s="32"/>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="21"/>
-      <c r="B29" s="20"/>
-      <c r="C29" s="21"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="21"/>
-      <c r="J29" s="21"/>
+      <c r="A29" s="26"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="27"/>
+      <c r="J29" s="28"/>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="19" t="s">
         <v>12</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="19" t="s">
         <v>12</v>
       </c>
       <c r="D30" s="1" t="s">
@@ -3414,13 +3338,13 @@
       <c r="F30" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H30" s="8" t="s">
+      <c r="H30" s="19" t="s">
         <v>12</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J30" s="8" t="s">
+      <c r="J30" s="19" t="s">
         <v>12</v>
       </c>
     </row>
@@ -3440,10 +3364,10 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="17.25" style="1" customWidth="1"/>
-    <col min="2" max="2" width="41.125" style="8" customWidth="1"/>
-    <col min="3" max="3" width="25.25" style="8" customWidth="1"/>
-    <col min="4" max="4" width="11.5" style="8" customWidth="1"/>
-    <col min="5" max="5" width="47" style="8" customWidth="1"/>
+    <col min="2" max="2" width="41.125" style="19" customWidth="1"/>
+    <col min="3" max="3" width="25.25" style="19" customWidth="1"/>
+    <col min="4" max="4" width="11.5" style="19" customWidth="1"/>
+    <col min="5" max="5" width="47" style="19" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="23" customHeight="1" spans="1:5">
@@ -3453,13 +3377,13 @@
       <c r="B1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="20" t="s">
         <v>63</v>
       </c>
     </row>
@@ -3467,16 +3391,16 @@
       <c r="A2" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="10" t="s">
+      <c r="B2" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="22">
         <v>45.5</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="21" t="s">
         <v>65</v>
       </c>
     </row>
@@ -3484,16 +3408,16 @@
       <c r="A3" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="22">
         <v>20.5</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="21" t="s">
         <v>69</v>
       </c>
     </row>
@@ -3501,16 +3425,16 @@
       <c r="A4" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="22">
         <v>39.8</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="21" t="s">
         <v>73</v>
       </c>
     </row>
@@ -3518,16 +3442,16 @@
       <c r="A5" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="10" t="s">
+      <c r="B5" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="22">
         <v>45.5</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="21" t="s">
         <v>75</v>
       </c>
     </row>
@@ -3535,50 +3459,50 @@
       <c r="A6" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="22">
         <v>20.5</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="21" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="7" ht="27" spans="1:5">
-      <c r="A7" s="5" t="s">
+    <row r="7" ht="27" customHeight="1" spans="1:5">
+      <c r="A7" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="22">
         <v>45.5</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="21" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="8" ht="27" spans="1:5">
-      <c r="A8" s="5" t="s">
+    <row r="8" ht="27" customHeight="1" spans="1:5">
+      <c r="A8" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="22">
         <v>10.8</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="21" t="s">
         <v>83</v>
       </c>
     </row>
@@ -3586,16 +3510,16 @@
       <c r="A9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="22">
         <v>25</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="21" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3603,16 +3527,16 @@
       <c r="A10" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="22">
         <v>23.9</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="21" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3620,16 +3544,16 @@
       <c r="A11" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="22">
         <v>22.7</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="21" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3637,50 +3561,50 @@
       <c r="A12" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="22">
         <v>102.3</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="21" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="22">
         <v>20.5</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="21" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="22">
         <v>30.7</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="21" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3688,50 +3612,50 @@
       <c r="A15" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="22">
         <v>56.8</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="21" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="22">
         <v>28.4</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="21" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="22">
         <v>68.2</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="21" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3739,16 +3663,16 @@
       <c r="A18" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="22">
         <v>22.7</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="21" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3756,16 +3680,16 @@
       <c r="A19" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="22">
         <v>56.8</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="21" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3773,50 +3697,50 @@
       <c r="A20" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="22">
         <v>90.9</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="21" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="22">
         <v>11.4</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="21" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="22">
         <v>54</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E22" s="21" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3824,34 +3748,34 @@
       <c r="A23" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="22">
         <v>45.5</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E23" s="21" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1" spans="1:5">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="15"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="25"/>
     </row>
     <row r="25" ht="16" customHeight="1" spans="1:5">
-      <c r="A25" s="16"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="18"/>
+      <c r="A25" s="26"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3865,15 +3789,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K69"/>
+  <dimension ref="A1:K75"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="15.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="30.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23" style="1" customWidth="1"/>
-    <col min="6" max="6" width="45.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="29.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="53.375" style="1" customWidth="1"/>
     <col min="7" max="7" width="46.125" style="1" customWidth="1"/>
     <col min="8" max="8" width="15.375" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.25" style="1" customWidth="1"/>
@@ -3881,7 +3805,7 @@
     <col min="11" max="11" width="8.625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:11">
+    <row r="1" ht="27" customHeight="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>118</v>
       </c>
@@ -3916,7 +3840,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="2" ht="94.5" spans="1:11">
+    <row r="2" ht="94.5" customHeight="1" spans="1:11">
       <c r="A2" s="3" t="s">
         <v>125</v>
       </c>
@@ -3951,7 +3875,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" ht="40.5" spans="1:11">
+    <row r="3" ht="40.5" customHeight="1" spans="1:11">
       <c r="A3" s="3" t="s">
         <v>125</v>
       </c>
@@ -3986,56 +3910,56 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" ht="27" spans="1:11">
-      <c r="A4" s="3" t="s">
+    <row r="4" ht="54" spans="1:11">
+      <c r="A4" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="D4" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="E4" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="7">
+        <v>45.5</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" ht="27" customHeight="1" spans="1:11">
+      <c r="A5" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="4">
-        <v>102.272727272727</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" ht="27" spans="1:11">
-      <c r="A5" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>141</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>142</v>
@@ -4044,10 +3968,10 @@
         <v>143</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I5" s="4">
-        <v>25</v>
+        <v>102.272727272727</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>29</v>
@@ -4056,68 +3980,68 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" ht="27" spans="1:11">
+    <row r="6" ht="27" customHeight="1" spans="1:11">
       <c r="A6" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>144</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>116</v>
+        <v>39</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G6" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="4">
+        <v>25</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" ht="27" customHeight="1" spans="1:11">
+      <c r="A7" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="4">
-        <v>45.4545454545455</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" ht="27" spans="1:11">
-      <c r="A7" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>116</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="I7" s="4">
-        <v>31.8181818181818</v>
+        <v>45.4545454545455</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>29</v>
@@ -4126,56 +4050,56 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1" spans="1:11">
+    <row r="8" ht="27" customHeight="1" spans="1:11">
       <c r="A8" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>29</v>
+        <v>140</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>149</v>
+        <v>29</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>150</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I8" s="4">
+        <v>31.8181818181818</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:11">
+      <c r="A9" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="I8" s="4">
-        <v>17.0454545454545</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" ht="40.5" spans="1:11">
-      <c r="A9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>156</v>
@@ -4184,30 +4108,30 @@
         <v>157</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="I9" s="4">
-        <v>96.5909090909091</v>
-      </c>
-      <c r="J9" s="3">
-        <v>0.25</v>
+        <v>17.0454545454545</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>131</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="10" ht="40.5" spans="1:11">
+    <row r="10" ht="40.5" customHeight="1" spans="1:11">
       <c r="A10" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>126</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>159</v>
+        <v>13</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>8</v>
@@ -4219,24 +4143,24 @@
         <v>161</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="I10" s="4">
         <v>96.5909090909091</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>131</v>
+      <c r="J10" s="3">
+        <v>0.25</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" ht="40.5" spans="1:11">
+    <row r="11" ht="40.5" customHeight="1" spans="1:11">
       <c r="A11" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>162</v>
@@ -4245,42 +4169,42 @@
         <v>163</v>
       </c>
       <c r="E11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" s="4">
+        <v>96.5909090909091</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" ht="40.5" customHeight="1" spans="1:11">
+      <c r="A12" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" s="4">
-        <v>90.9090909090909</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" ht="27" spans="1:11">
-      <c r="A12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>169</v>
@@ -4289,30 +4213,30 @@
         <v>170</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="I12" s="4">
-        <v>11.3636363636364</v>
+        <v>90.9090909090909</v>
       </c>
       <c r="J12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" ht="27" customHeight="1" spans="1:11">
+      <c r="A13" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" ht="27" spans="1:11">
-      <c r="A13" s="3" t="s">
-        <v>167</v>
-      </c>
       <c r="B13" s="3" t="s">
-        <v>126</v>
+        <v>172</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>172</v>
+        <v>38</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>41</v>
@@ -4327,43 +4251,43 @@
         <v>52</v>
       </c>
       <c r="I13" s="4">
+        <v>11.3636363636364</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" ht="27" customHeight="1" spans="1:11">
+      <c r="A14" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="I14" s="4">
         <v>18.1818181818182</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" ht="67.5" spans="1:11">
-      <c r="A14" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="I14" s="4">
-        <v>11.3636363636364</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>29</v>
       </c>
@@ -4371,12 +4295,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" ht="54" spans="1:11">
+    <row r="15" ht="67.5" customHeight="1" spans="1:11">
       <c r="A15" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>29</v>
@@ -4385,42 +4309,42 @@
         <v>179</v>
       </c>
       <c r="E15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>9</v>
-      </c>
       <c r="I15" s="4">
-        <v>77.2727272727273</v>
+        <v>11.3636363636364</v>
       </c>
       <c r="J15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" ht="54" customHeight="1" spans="1:11">
+      <c r="A16" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" ht="54" spans="1:11">
-      <c r="A16" s="3" t="s">
-        <v>167</v>
-      </c>
       <c r="B16" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
         <v>184</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>185</v>
@@ -4429,81 +4353,81 @@
         <v>186</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>178</v>
+        <v>9</v>
       </c>
       <c r="I16" s="4">
+        <v>77.2727272727273</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" ht="54" customHeight="1" spans="1:11">
+      <c r="A17" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="I17" s="4">
         <v>18.1818181818182</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" ht="40.5" spans="1:11">
-      <c r="A17" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="E17" s="3" t="s">
+      <c r="J17" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" ht="40.5" customHeight="1" spans="1:11">
+      <c r="A18" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="H17" s="3" t="s">
+      <c r="F18" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="I17" s="4">
+      <c r="I18" s="4">
         <v>21.0227272727273</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" ht="27" spans="1:11">
-      <c r="A18" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" s="4">
-        <v>34.0909090909091</v>
-      </c>
       <c r="J18" s="3" t="s">
         <v>29</v>
       </c>
@@ -4511,161 +4435,161 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" ht="54" spans="1:11">
+    <row r="19" ht="27" customHeight="1" spans="1:11">
       <c r="A19" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>193</v>
+        <v>29</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>194</v>
       </c>
       <c r="E19" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="G19" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="4">
+        <v>34.0909090909091</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" ht="54" customHeight="1" spans="1:11">
+      <c r="A20" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="I19" s="4">
+      <c r="E20" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="I20" s="4">
         <v>17.0454545454545</v>
       </c>
-      <c r="J19" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="K19" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" ht="27" spans="1:11">
-      <c r="A20" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="K20" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" ht="67.5" spans="1:11">
+      <c r="A21" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I20" s="4">
-        <v>45.4545454545455</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K20" s="3" t="s">
+      <c r="D21" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="21" ht="27" spans="1:11">
-      <c r="A21" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B21" s="3" t="s">
+      <c r="G21" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="H21" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I21" s="7">
+        <v>23.9</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" ht="81" spans="1:11">
+      <c r="A22" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="B22" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="C22" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="D22" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="F22" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="I21" s="4">
-        <v>28.4090909090909</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" ht="54" spans="1:11">
-      <c r="A22" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C22" s="3" t="s">
+      <c r="G22" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="H22" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="F22" s="3" t="s">
+      <c r="I22" s="11">
+        <v>39.8</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" ht="27" customHeight="1" spans="1:11">
+      <c r="A23" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="B23" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>214</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="I22" s="4">
-        <v>34.0909090909091</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="23" ht="54" spans="1:11">
-      <c r="A23" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>215</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>216</v>
@@ -4674,220 +4598,220 @@
         <v>217</v>
       </c>
       <c r="H23" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I23" s="4">
+        <v>45.4545454545455</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K23" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="I23" s="4">
+    </row>
+    <row r="24" ht="27" customHeight="1" spans="1:11">
+      <c r="A24" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="I24" s="4">
+        <v>28.4090909090909</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" ht="54" customHeight="1" spans="1:11">
+      <c r="A25" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I25" s="4">
+        <v>34.0909090909091</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" ht="54" customHeight="1" spans="1:11">
+      <c r="A26" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="I26" s="4">
         <v>20.4545454545455</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="24" ht="40.5" spans="1:11">
-      <c r="A24" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C24" s="3" t="s">
+      <c r="J26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" ht="40.5" customHeight="1" spans="1:11">
+      <c r="A27" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E27" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="F27" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I27" s="4">
+        <v>20.4545454545455</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" ht="40.5" customHeight="1" spans="1:11">
+      <c r="A28" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="I24" s="4">
-        <v>20.4545454545455</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="25" ht="40.5" spans="1:11">
-      <c r="A25" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C25" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D28" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="F28" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="I28" s="4">
+        <v>30.6818181818182</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" ht="54" customHeight="1" spans="1:11">
+      <c r="A29" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="I25" s="4">
-        <v>30.6818181818182</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" ht="54" spans="1:11">
-      <c r="A26" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C26" s="5" t="s">
+      <c r="C29" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="I26" s="4">
+      <c r="F29" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="I29" s="4">
         <v>45.4545454545455</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="27" ht="54" spans="1:11">
-      <c r="A27" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="H27" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I27" s="4">
-        <v>10.7954545454545</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="28" ht="40.5" spans="1:11">
-      <c r="A28" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I28" s="4">
-        <v>28.4090909090909</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="29" ht="40.5" spans="1:11">
-      <c r="A29" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="I29" s="4">
-        <v>56.8181818181818</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>131</v>
@@ -4896,138 +4820,138 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" ht="40.5" spans="1:11">
+    <row r="30" ht="54" customHeight="1" spans="1:11">
       <c r="A30" s="3" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>98</v>
+        <v>219</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
+      </c>
+      <c r="H30" s="3">
+        <v>1200</v>
       </c>
       <c r="I30" s="4">
-        <v>28.4090909090909</v>
+        <v>10.7954545454545</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>131</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" ht="54" spans="1:11">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="31" ht="40.5" customHeight="1" spans="1:11">
       <c r="A31" s="3" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>29</v>
+        <v>219</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>101</v>
+        <v>242</v>
       </c>
       <c r="D31" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I31" s="4">
+        <v>28.4090909090909</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" ht="40.5" customHeight="1" spans="1:11">
+      <c r="A32" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="I32" s="4">
+        <v>56.8181818181818</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" ht="40.5" customHeight="1" spans="1:11">
+      <c r="A33" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="I31" s="4">
-        <v>68.1818181818182</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32" ht="54" spans="1:11">
-      <c r="A32" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="I32" s="4">
-        <v>45.4545454545455</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" ht="40.5" spans="1:11">
-      <c r="A33" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>247</v>
-      </c>
       <c r="E33" s="3" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>12</v>
+        <v>252</v>
       </c>
       <c r="I33" s="4">
-        <v>56.8181818181818</v>
+        <v>28.4090909090909</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>131</v>
@@ -5036,33 +4960,33 @@
         <v>29</v>
       </c>
     </row>
-    <row r="34" ht="40.5" spans="1:11">
+    <row r="34" ht="54" customHeight="1" spans="1:11">
       <c r="A34" s="3" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>250</v>
+        <v>29</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>251</v>
+        <v>101</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>252</v>
+        <v>99</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F34" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G34" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="H34" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="H34" s="3" t="s">
-        <v>255</v>
-      </c>
       <c r="I34" s="4">
-        <v>31.8181818181818</v>
+        <v>68.1818181818182</v>
       </c>
       <c r="J34" s="3" t="s">
         <v>131</v>
@@ -5071,21 +4995,21 @@
         <v>29</v>
       </c>
     </row>
-    <row r="35" ht="81" spans="1:11">
+    <row r="35" ht="54" customHeight="1" spans="1:11">
       <c r="A35" s="3" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>29</v>
-      </c>
       <c r="D35" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>257</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>258</v>
@@ -5094,185 +5018,185 @@
         <v>259</v>
       </c>
       <c r="H35" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="I35" s="4">
+        <v>45.4545454545455</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" ht="40.5" customHeight="1" spans="1:11">
+      <c r="A36" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I36" s="4">
+        <v>56.8181818181818</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" ht="40.5" customHeight="1" spans="1:11">
+      <c r="A37" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="I37" s="4">
+        <v>31.8181818181818</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" ht="81" customHeight="1" spans="1:11">
+      <c r="A38" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="H38" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="I35" s="4">
+      <c r="I38" s="4">
         <v>34.0909090909091</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="36" ht="54" spans="1:11">
-      <c r="A36" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="E36" s="3" t="s">
+      <c r="J38" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="39" ht="54" customHeight="1" spans="1:11">
+      <c r="A39" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="E39" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F36" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="H36" s="3" t="s">
+      <c r="F39" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H39" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I36" s="4">
+      <c r="I39" s="4">
         <v>25</v>
       </c>
-      <c r="J36" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="37" ht="54" spans="1:11">
-      <c r="A37" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I37" s="4">
-        <v>45.4545454545455</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="38" ht="40.5" spans="1:11">
-      <c r="A38" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I38" s="4">
-        <v>22.7272727272727</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="39" ht="54" spans="1:11">
-      <c r="A39" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="C39" s="3" t="s">
+      <c r="J39" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40" ht="54" customHeight="1" spans="1:11">
+      <c r="A40" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="I39" s="4">
-        <v>102.272727272727</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="40" ht="54" spans="1:11">
-      <c r="A40" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>269</v>
-      </c>
       <c r="C40" s="3" t="s">
-        <v>274</v>
+        <v>29</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>116</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="I40" s="4">
-        <v>53.4090909090909</v>
+        <v>45.4545454545455</v>
       </c>
       <c r="J40" s="3" t="s">
         <v>29</v>
@@ -5281,278 +5205,278 @@
         <v>29</v>
       </c>
     </row>
-    <row r="41" ht="67.5" spans="1:11">
+    <row r="41" ht="40.5" customHeight="1" spans="1:11">
       <c r="A41" s="3" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>277</v>
+        <v>270</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>279</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F41" s="6" t="s">
-        <v>279</v>
+      <c r="F41" s="3" t="s">
+        <v>281</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>11</v>
       </c>
       <c r="I41" s="4">
+        <v>22.7272727272727</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="42" ht="54" customHeight="1" spans="1:11">
+      <c r="A42" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I42" s="4">
+        <v>102.272727272727</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="43" ht="54" customHeight="1" spans="1:11">
+      <c r="A43" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I43" s="4">
+        <v>53.4090909090909</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="44" ht="67.5" customHeight="1" spans="1:11">
+      <c r="A44" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I44" s="4">
         <v>28.4090909090909</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="42" ht="67.5" spans="1:11">
-      <c r="A42" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="E42" s="3" t="s">
+      <c r="J44" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="45" ht="67.5" customHeight="1" spans="1:11">
+      <c r="A45" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="E45" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="H42" s="3" t="s">
+      <c r="F45" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="H45" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I42" s="4">
+      <c r="I45" s="4">
         <v>45.4545454545455</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="43" ht="67.5" spans="1:11">
-      <c r="A43" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D43" s="3" t="s">
+      <c r="J45" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="46" ht="67.5" customHeight="1" spans="1:11">
+      <c r="A46" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="C46" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="E46" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="H43" s="3" t="s">
+      <c r="F46" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="H46" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="I43" s="4">
+      <c r="I46" s="4">
         <v>22.7272727272727</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="44" ht="40.5" spans="1:11">
-      <c r="A44" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="D44" s="3" t="s">
+      <c r="J46" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="47" ht="40.5" customHeight="1" spans="1:11">
+      <c r="A47" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="E47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="H44" s="3" t="s">
+      <c r="F47" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="H47" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="I44" s="4">
+      <c r="I47" s="4">
         <v>68.1818181818182</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="45" ht="40.5" spans="1:11">
-      <c r="A45" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="D45" s="3" t="s">
+      <c r="J47" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="48" ht="40.5" customHeight="1" spans="1:11">
+      <c r="A48" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="E48" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="H45" s="3" t="s">
+      <c r="F48" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="H48" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="I45" s="4">
-        <v>20.4545454545455</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="46" ht="54" spans="1:11">
-      <c r="A46" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I46" s="4">
-        <v>37.5</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="47" ht="40.5" spans="1:11">
-      <c r="A47" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="I47" s="4">
-        <v>56.8181818181818</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="48" ht="54" spans="1:11">
-      <c r="A48" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="I48" s="4">
-        <v>28.4090909090909</v>
+        <v>22.7</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>29</v>
@@ -5563,217 +5487,217 @@
     </row>
     <row r="49" ht="40.5" spans="1:11">
       <c r="A49" s="3" t="s">
-        <v>301</v>
+        <v>213</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>29</v>
+        <v>283</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>302</v>
+        <v>29</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>304</v>
+        <v>116</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I49" s="4">
-        <v>20.4545454545455</v>
+        <v>37.5</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>131</v>
+        <v>29</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="50" ht="40.5" spans="1:11">
+    <row r="50" ht="40.5" customHeight="1" spans="1:11">
       <c r="A50" s="3" t="s">
-        <v>301</v>
+        <v>213</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>29</v>
+        <v>283</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>307</v>
+        <v>105</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>303</v>
+        <v>106</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>9</v>
       </c>
       <c r="I50" s="4">
-        <v>20.4545454545455</v>
+        <v>56.8181818181818</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="K50" s="7">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="51" ht="27" spans="1:11">
-      <c r="A51" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="B51" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="51" ht="45" customHeight="1" spans="1:11">
+      <c r="A51" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C51" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="D51" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E51" s="10" t="s">
         <v>311</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="F51" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="E51" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F51" s="3" t="s">
+      <c r="G51" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="I51" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="J51" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K51" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="52" ht="54" customHeight="1" spans="1:11">
+      <c r="A52" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="G51" s="3" t="s">
+      <c r="B52" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="H51" s="3" t="s">
+      <c r="E52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="I51" s="4">
-        <v>18.1818181818182</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K51" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="52" ht="40.5" spans="1:11">
-      <c r="A52" s="3" t="s">
+      <c r="G52" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C52" s="3" t="s">
+      <c r="H52" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I52" s="4">
+        <v>28.4090909090909</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="53" ht="108" spans="1:11">
+      <c r="A53" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="B53" s="13" t="s">
         <v>317</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="C53" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F52" s="3" t="s">
+      <c r="D53" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E53" s="10" t="s">
         <v>319</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="I52" s="4">
-        <v>90.9090909090909</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="53" ht="67.5" spans="1:11">
-      <c r="A53" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C53" s="3" t="s">
+      <c r="F53" s="13" t="s">
         <v>320</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="G53" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="E53" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="F53" s="3" t="s">
+      <c r="H53" s="13" t="s">
         <v>322</v>
       </c>
-      <c r="G53" s="3" t="s">
+      <c r="I53" s="15">
+        <v>45.5</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K53" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="54" ht="81" spans="1:11">
+      <c r="A54" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C54" s="16" t="s">
         <v>323</v>
       </c>
-      <c r="H53" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I53" s="4">
-        <v>28.4090909090909</v>
-      </c>
-      <c r="J53" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K53" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="54" ht="40.5" spans="1:11">
-      <c r="A54" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C54" s="3" t="s">
+      <c r="D54" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E54" s="17" t="s">
+        <v>319</v>
+      </c>
+      <c r="F54" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="G54" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="E54" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" s="3" t="s">
+      <c r="H54" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="G54" s="3" t="s">
+      <c r="I54" s="7">
+        <v>45.5</v>
+      </c>
+      <c r="J54" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K54" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="55" ht="40.5" customHeight="1" spans="1:11">
+      <c r="A55" s="3" t="s">
         <v>327</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I54" s="4">
-        <v>11.3636363636364</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="55" ht="40.5" spans="1:11">
-      <c r="A55" s="3" t="s">
-        <v>316</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>29</v>
@@ -5782,80 +5706,80 @@
         <v>328</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>8</v>
+        <v>330</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="G55" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I55" s="4">
+        <v>20.4545454545455</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="56" ht="40.5" customHeight="1" spans="1:11">
+      <c r="A56" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D56" s="3" t="s">
         <v>329</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I55" s="4">
-        <v>53.9772727272727</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="K55" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="56" ht="27" spans="1:11">
-      <c r="A56" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>332</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>104</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G56" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I56" s="4">
+        <v>20.4545454545455</v>
+      </c>
+      <c r="J56" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="H56" s="3" t="s">
+      <c r="K56" s="18">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="57" ht="27" customHeight="1" spans="1:11">
+      <c r="A57" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="I56" s="4">
-        <v>56.8181818181818</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="K56" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="57" ht="27" spans="1:11">
-      <c r="A57" s="3" t="s">
-        <v>330</v>
-      </c>
       <c r="B57" s="3" t="s">
-        <v>29</v>
+        <v>336</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>338</v>
+        <v>39</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>339</v>
@@ -5864,103 +5788,103 @@
         <v>340</v>
       </c>
       <c r="H57" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="I57" s="4">
+        <v>18.1818181818182</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="58" ht="40.5" customHeight="1" spans="1:11">
+      <c r="A58" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I58" s="4">
+        <v>90.9090909090909</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="59" ht="67.5" customHeight="1" spans="1:11">
+      <c r="A59" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="H59" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I57" s="4">
-        <v>20.4545454545455</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="58" ht="40.5" spans="1:11">
-      <c r="A58" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F58" s="3" t="s">
+      <c r="I59" s="4">
+        <v>28.4090909090909</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="60" ht="40.5" customHeight="1" spans="1:11">
+      <c r="A60" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I58" s="4">
-        <v>15.9090909090909</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="59" ht="54" spans="1:11">
-      <c r="A59" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="I59" s="4">
-        <v>29.5454545454545</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="60" ht="40.5" spans="1:11">
-      <c r="A60" s="3" t="s">
-        <v>348</v>
-      </c>
       <c r="B60" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>349</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>350</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>116</v>
+        <v>10</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>351</v>
@@ -5969,115 +5893,115 @@
         <v>352</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="I60" s="4">
-        <v>40.9090909090909</v>
+        <v>11.3636363636364</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>29</v>
+        <v>175</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="61" ht="27" spans="1:11">
+    <row r="61" ht="40.5" customHeight="1" spans="1:11">
       <c r="A61" s="3" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="B61" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="D61" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="G61" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="H61" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I61" s="4">
+        <v>53.9772727272727</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="62" ht="27" customHeight="1" spans="1:11">
+      <c r="A62" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="E61" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F61" s="3" t="s">
+      <c r="B62" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="G61" s="3" t="s">
+      <c r="D62" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="H61" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I61" s="4">
-        <v>14.7727272727273</v>
-      </c>
-      <c r="J61" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K61" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="62" ht="67.5" spans="1:11">
-      <c r="A62" s="3" t="s">
+      <c r="E62" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F62" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="B62" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D62" s="6" t="s">
+      <c r="G62" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="E62" s="3" t="s">
+      <c r="H62" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="F62" s="6" t="s">
+      <c r="I62" s="4">
+        <v>56.8181818181818</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="63" ht="27" customHeight="1" spans="1:11">
+      <c r="A63" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="G62" s="3" t="s">
+      <c r="D63" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I62" s="4">
-        <v>5.68181818181818</v>
-      </c>
-      <c r="J62" s="3" t="s">
+      <c r="E63" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="63" ht="67.5" spans="1:11">
-      <c r="A63" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D63" s="6" t="s">
+      <c r="F63" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="E63" s="3" t="s">
+      <c r="G63" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="F63" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>362</v>
-      </c>
       <c r="H63" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I63" s="4">
-        <v>5.68181818181818</v>
+        <v>20.4545454545455</v>
       </c>
       <c r="J63" s="3" t="s">
         <v>131</v>
@@ -6086,103 +6010,103 @@
         <v>29</v>
       </c>
     </row>
-    <row r="64" ht="40.5" spans="1:11">
+    <row r="64" ht="40.5" customHeight="1" spans="1:11">
       <c r="A64" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D64" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="B64" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C64" s="3" t="s">
+      <c r="E64" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F64" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="D64" s="3" t="s">
+      <c r="G64" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="E64" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="F64" s="3" t="s">
+      <c r="H64" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I64" s="4">
+        <v>15.9090909090909</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="65" ht="54" customHeight="1" spans="1:11">
+      <c r="A65" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="G64" s="3" t="s">
+      <c r="C65" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D65" s="3" t="s">
         <v>370</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="I64" s="4">
-        <v>12.5</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="K64" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="65" ht="43" customHeight="1" spans="1:11">
-      <c r="A65" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F65" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="I65" s="4">
+        <v>29.5454545454545</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="66" ht="40.5" customHeight="1" spans="1:11">
+      <c r="A66" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D66" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="G65" s="3" t="s">
+      <c r="E66" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F66" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="H65" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="I65" s="4">
-        <v>11.3636363636364</v>
-      </c>
-      <c r="J65" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K65" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="66" ht="81" spans="1:11">
-      <c r="A66" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D66" s="3" t="s">
+      <c r="G66" s="3" t="s">
         <v>377</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>379</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>58</v>
       </c>
       <c r="I66" s="4">
-        <v>17.0454545454545</v>
+        <v>40.9090909090909</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>29</v>
@@ -6191,108 +6115,318 @@
         <v>29</v>
       </c>
     </row>
-    <row r="67" ht="35" customHeight="1" spans="1:11">
+    <row r="67" ht="27" customHeight="1" spans="1:11">
       <c r="A67" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="D67" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="E67" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F67" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="C67" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D67" s="3" t="s">
+      <c r="G67" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="E67" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F67" s="3" t="s">
+      <c r="H67" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I67" s="4">
+        <v>14.7727272727273</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="68" ht="67.5" customHeight="1" spans="1:11">
+      <c r="A68" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="G67" s="3" t="s">
+      <c r="B68" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D68" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="H67" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I67" s="4">
-        <v>12.5</v>
-      </c>
-      <c r="J67" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="K67" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="68" ht="40.5" spans="1:11">
-      <c r="A68" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="B68" s="3" t="s">
+      <c r="E68" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C68" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D68" s="3" t="s">
+      <c r="F68" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="E68" s="3" t="s">
+      <c r="G68" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="F68" s="3" t="s">
+      <c r="H68" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I68" s="4">
+        <v>5.68181818181818</v>
+      </c>
+      <c r="J68" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="G68" s="3" t="s">
+      <c r="K68" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="69" ht="67.5" customHeight="1" spans="1:11">
+      <c r="A69" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D69" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="H68" s="3" t="s">
+      <c r="E69" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="I68" s="4">
-        <v>9.09090909090909</v>
-      </c>
-      <c r="J68" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="K68" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="69" ht="67.5" spans="1:11">
-      <c r="A69" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>151</v>
-      </c>
       <c r="F69" s="3" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>395</v>
+        <v>14</v>
       </c>
       <c r="I69" s="4">
-        <v>17.0454545454545</v>
+        <v>5.68181818181818</v>
       </c>
       <c r="J69" s="3" t="s">
         <v>131</v>
       </c>
       <c r="K69" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="70" ht="40.5" customHeight="1" spans="1:11">
+      <c r="A70" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="I70" s="4">
+        <v>12.5</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="71" ht="43" customHeight="1" spans="1:11">
+      <c r="A71" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I71" s="4">
+        <v>11.3636363636364</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K71" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="72" ht="81" customHeight="1" spans="1:11">
+      <c r="A72" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I72" s="4">
+        <v>17.0454545454545</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="73" ht="35" customHeight="1" spans="1:11">
+      <c r="A73" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I73" s="4">
+        <v>12.5</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="K73" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="74" ht="40.5" customHeight="1" spans="1:11">
+      <c r="A74" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="I74" s="4">
+        <v>9.09090909090909</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="75" ht="67.5" customHeight="1" spans="1:11">
+      <c r="A75" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="I75" s="4">
+        <v>17.0454545454545</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="K75" s="3" t="s">
         <v>29</v>
       </c>
     </row>

--- a/合并产品信息表修改后.xlsx
+++ b/合并产品信息表修改后.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="417">
   <si>
     <t>序号</t>
   </si>
@@ -442,9 +442,6 @@
     <t>注射600公斤体重</t>
   </si>
   <si>
-    <t>畅健®</t>
-  </si>
-  <si>
     <t>无抗高效广谱抑菌口服液</t>
   </si>
   <si>
@@ -1005,7 +1002,7 @@
     <t>预防水禽传染性浆膜炎</t>
   </si>
   <si>
-    <t>浆小白</t>
+    <t>浆小白（水禽）</t>
   </si>
   <si>
     <t>250ml/瓶×40瓶/箱</t>
@@ -1023,9 +1020,6 @@
     <t>2500只</t>
   </si>
   <si>
-    <t>浆小白（清解合剂）</t>
-  </si>
-  <si>
     <t>1、靶向益生菌发酵产生的荚膜多糖类似物刺激机体产生黏膜免疫抗体，起到预防鸭疫菌侵入机体的作用。
 2、中药清解合剂具有清热凉血功效，可有效预防包心包肝的发生。
 3、用于预防肉鸡、蛋鸡、种鸡的鸭疫里默氏杆菌感染。 
@@ -1104,9 +1098,6 @@
     <t>兑水800斤，饮用6-8小时，连用4-5天。</t>
   </si>
   <si>
-    <t>(中药)羡康100g</t>
-  </si>
-  <si>
     <t>天然植物饲料原料 干姜粗提物</t>
   </si>
   <si>
@@ -1115,9 +1106,6 @@
   </si>
   <si>
     <t>本品 100g兑水400斤，全天量集中饮用 8小时，连用 4-5天</t>
-  </si>
-  <si>
-    <t>(中药) 羡康500g</t>
   </si>
   <si>
     <t>本品 500g兑水2500斤，全天量集中饮用 8小时，连用 4-5天</t>
@@ -1350,13 +1338,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF2E2E2E"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF2E2E2E"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -2069,7 +2057,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2086,21 +2074,15 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2110,16 +2092,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -2502,27 +2481,27 @@
   <dimension ref="A1:J30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="9" style="19" customWidth="1"/>
+    <col min="1" max="1" width="9" style="16" customWidth="1"/>
     <col min="2" max="2" width="29.625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.125" style="19" customWidth="1"/>
+    <col min="3" max="3" width="13.125" style="16" customWidth="1"/>
     <col min="4" max="4" width="17.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.25" style="1" customWidth="1"/>
     <col min="7" max="7" width="18" style="1" customWidth="1"/>
-    <col min="8" max="8" width="7.125" style="19" customWidth="1"/>
+    <col min="8" max="8" width="7.125" style="16" customWidth="1"/>
     <col min="9" max="9" width="10.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.625" style="19" customWidth="1"/>
+    <col min="10" max="10" width="12.625" style="16" customWidth="1"/>
     <col min="11" max="14" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="27" customHeight="1" spans="1:10">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -2537,24 +2516,24 @@
       <c r="G1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="H1" s="17" t="s">
         <v>4</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="20" t="s">
+      <c r="J1" s="17" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="21">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="29">
+      <c r="C2" s="26">
         <v>0.2</v>
       </c>
       <c r="D2" s="3" t="s">
@@ -2570,25 +2549,25 @@
       <c r="G2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="18" t="s">
         <v>11</v>
       </c>
       <c r="I2" s="4">
         <f>5.3/0.88</f>
         <v>6.02272727272727</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="21">
+      <c r="A3" s="18">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="29">
+      <c r="C3" s="26">
         <v>0.5</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -2604,23 +2583,23 @@
       <c r="G3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="21" t="s">
+      <c r="H3" s="18" t="s">
         <v>15</v>
       </c>
       <c r="I3" s="4">
         <f>23.3/0.88</f>
         <v>26.4772727272727</v>
       </c>
-      <c r="J3" s="21"/>
+      <c r="J3" s="18"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="21">
+      <c r="A4" s="18">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="26">
         <v>0.5</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -2636,23 +2615,23 @@
       <c r="G4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="21" t="s">
+      <c r="H4" s="18" t="s">
         <v>11</v>
       </c>
       <c r="I4" s="4">
         <f>3.7/0.88</f>
         <v>4.20454545454546</v>
       </c>
-      <c r="J4" s="21"/>
+      <c r="J4" s="18"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="21">
+      <c r="A5" s="18">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="26">
         <v>0.3</v>
       </c>
       <c r="D5" s="3" t="s">
@@ -2668,25 +2647,25 @@
       <c r="G5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="H5" s="18" t="s">
         <v>19</v>
       </c>
       <c r="I5" s="4">
         <f>8.6/0.88</f>
         <v>9.77272727272727</v>
       </c>
-      <c r="J5" s="21" t="s">
+      <c r="J5" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="21">
+      <c r="A6" s="18">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" s="26" t="s">
         <v>21</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -2702,25 +2681,25 @@
       <c r="G6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="H6" s="18" t="s">
         <v>15</v>
       </c>
       <c r="I6" s="4">
         <f>5.1/0.88</f>
         <v>5.79545454545454</v>
       </c>
-      <c r="J6" s="21" t="s">
+      <c r="J6" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="21">
+      <c r="A7" s="18">
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" s="26" t="s">
         <v>21</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -2736,23 +2715,23 @@
       <c r="G7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="21" t="s">
+      <c r="H7" s="18" t="s">
         <v>15</v>
       </c>
       <c r="I7" s="4">
         <f>5.1/0.88</f>
         <v>5.79545454545454</v>
       </c>
-      <c r="J7" s="21"/>
+      <c r="J7" s="18"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="21">
+      <c r="A8" s="18">
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="26">
         <v>0.325</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -2768,25 +2747,25 @@
       <c r="G8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="21" t="s">
+      <c r="H8" s="18" t="s">
         <v>19</v>
       </c>
       <c r="I8" s="4">
         <f>6.9/0.88</f>
         <v>7.84090909090909</v>
       </c>
-      <c r="J8" s="21" t="s">
+      <c r="J8" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="21">
+      <c r="A9" s="18">
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="26" t="s">
         <v>27</v>
       </c>
       <c r="D9" s="3" t="s">
@@ -2808,18 +2787,18 @@
       <c r="I9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="J9" s="21" t="s">
+      <c r="J9" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="21">
+      <c r="A10" s="18">
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" s="26" t="s">
         <v>31</v>
       </c>
       <c r="D10" s="3" t="s">
@@ -2841,18 +2820,18 @@
       <c r="I10" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="J10" s="21" t="s">
+      <c r="J10" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="21">
+      <c r="A11" s="18">
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="26">
         <v>0.1</v>
       </c>
       <c r="D11" s="3" t="s">
@@ -2868,23 +2847,23 @@
       <c r="G11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H11" s="21" t="s">
+      <c r="H11" s="18" t="s">
         <v>35</v>
       </c>
       <c r="I11" s="4">
         <f>5.4/0.88</f>
         <v>6.13636363636364</v>
       </c>
-      <c r="J11" s="21"/>
+      <c r="J11" s="18"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="21">
+      <c r="A12" s="18">
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="26">
         <v>0.2</v>
       </c>
       <c r="D12" s="3" t="s">
@@ -2900,25 +2879,25 @@
       <c r="G12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H12" s="21" t="s">
+      <c r="H12" s="18" t="s">
         <v>11</v>
       </c>
       <c r="I12" s="4">
         <f>4.1/0.88</f>
         <v>4.65909090909091</v>
       </c>
-      <c r="J12" s="21" t="s">
+      <c r="J12" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="21">
+      <c r="A13" s="18">
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="26">
         <v>0.12</v>
       </c>
       <c r="D13" s="3" t="s">
@@ -2934,25 +2913,25 @@
       <c r="G13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="21" t="s">
+      <c r="H13" s="18" t="s">
         <v>11</v>
       </c>
       <c r="I13" s="4">
         <f>5.2/0.88</f>
         <v>5.90909090909091</v>
       </c>
-      <c r="J13" s="21" t="s">
+      <c r="J13" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="21">
+      <c r="A14" s="18">
         <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="26">
         <v>0.25</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -2968,25 +2947,25 @@
       <c r="G14" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H14" s="21" t="s">
+      <c r="H14" s="18" t="s">
         <v>42</v>
       </c>
       <c r="I14" s="4">
         <f>13.3/0.88</f>
         <v>15.1136363636364</v>
       </c>
-      <c r="J14" s="21" t="s">
+      <c r="J14" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="21">
+      <c r="A15" s="18">
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="26">
         <v>0.5</v>
       </c>
       <c r="D15" s="3" t="s">
@@ -3002,25 +2981,25 @@
       <c r="G15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H15" s="21" t="s">
+      <c r="H15" s="18" t="s">
         <v>44</v>
       </c>
       <c r="I15" s="4">
         <f>21.1/0.88</f>
         <v>23.9772727272727</v>
       </c>
-      <c r="J15" s="21" t="s">
+      <c r="J15" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="21">
+      <c r="A16" s="18">
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="26">
         <v>0.2</v>
       </c>
       <c r="D16" s="3" t="s">
@@ -3036,25 +3015,25 @@
       <c r="G16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H16" s="21" t="s">
+      <c r="H16" s="18" t="s">
         <v>44</v>
       </c>
       <c r="I16" s="4">
         <f>10.7/0.88</f>
         <v>12.1590909090909</v>
       </c>
-      <c r="J16" s="21" t="s">
+      <c r="J16" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="17" ht="27" customHeight="1" spans="1:10">
-      <c r="A17" s="21">
+      <c r="A17" s="18">
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" s="26" t="s">
         <v>47</v>
       </c>
       <c r="D17" s="3" t="s">
@@ -3070,25 +3049,25 @@
       <c r="G17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H17" s="21" t="s">
+      <c r="H17" s="18" t="s">
         <v>11</v>
       </c>
       <c r="I17" s="4">
         <f>8.1/0.88</f>
         <v>9.20454545454545</v>
       </c>
-      <c r="J17" s="21" t="s">
+      <c r="J17" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="21">
+      <c r="A18" s="18">
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" s="26" t="s">
         <v>49</v>
       </c>
       <c r="D18" s="3" t="s">
@@ -3103,25 +3082,25 @@
       <c r="G18" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H18" s="21" t="s">
+      <c r="H18" s="18" t="s">
         <v>34</v>
       </c>
       <c r="I18" s="4">
         <f>27.2/0.88</f>
         <v>30.9090909090909</v>
       </c>
-      <c r="J18" s="21" t="s">
+      <c r="J18" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="19" ht="27" customHeight="1" spans="1:10">
-      <c r="A19" s="21">
+      <c r="A19" s="18">
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="26">
         <v>0.3</v>
       </c>
       <c r="D19" s="3" t="s">
@@ -3136,25 +3115,25 @@
       <c r="G19" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H19" s="21" t="s">
+      <c r="H19" s="18" t="s">
         <v>52</v>
       </c>
       <c r="I19" s="4">
         <f>10.3/0.88</f>
         <v>11.7045454545455</v>
       </c>
-      <c r="J19" s="21" t="s">
+      <c r="J19" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="20" ht="27" customHeight="1" spans="1:10">
-      <c r="A20" s="21">
+      <c r="A20" s="18">
         <v>18</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="26">
         <v>0.3</v>
       </c>
       <c r="D20" s="3" t="s">
@@ -3169,25 +3148,25 @@
       <c r="G20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H20" s="21" t="s">
+      <c r="H20" s="18" t="s">
         <v>52</v>
       </c>
       <c r="I20" s="4">
         <f>9/0.88</f>
         <v>10.2272727272727</v>
       </c>
-      <c r="J20" s="21" t="s">
+      <c r="J20" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="21">
+      <c r="A21" s="18">
         <v>19</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="26">
         <v>0.3</v>
       </c>
       <c r="D21" s="3" t="s">
@@ -3202,25 +3181,25 @@
       <c r="G21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H21" s="21" t="s">
+      <c r="H21" s="18" t="s">
         <v>55</v>
       </c>
       <c r="I21" s="4">
         <f>7.8/0.88</f>
         <v>8.86363636363636</v>
       </c>
-      <c r="J21" s="21" t="s">
+      <c r="J21" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="21">
+      <c r="A22" s="18">
         <v>20</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="26">
         <v>0.1</v>
       </c>
       <c r="D22" s="3" t="s">
@@ -3242,16 +3221,16 @@
       <c r="I22" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="J22" s="21"/>
+      <c r="J22" s="18"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="21">
+      <c r="A23" s="18">
         <v>21</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C23" s="29">
+      <c r="C23" s="26">
         <v>0.8</v>
       </c>
       <c r="D23" s="3" t="s">
@@ -3266,67 +3245,67 @@
       <c r="G23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H23" s="21" t="s">
+      <c r="H23" s="18" t="s">
         <v>58</v>
       </c>
       <c r="I23" s="4">
         <f>27.8/0.88</f>
         <v>31.5909090909091</v>
       </c>
-      <c r="J23" s="21" t="s">
+      <c r="J23" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="30" t="s">
+      <c r="A24" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="24"/>
-      <c r="I24" s="24"/>
-      <c r="J24" s="25"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="22"/>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="31"/>
-      <c r="J25" s="32"/>
+      <c r="A25" s="28"/>
+      <c r="J25" s="29"/>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="31"/>
-      <c r="J26" s="32"/>
+      <c r="A26" s="28"/>
+      <c r="J26" s="29"/>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="31"/>
-      <c r="J27" s="32"/>
+      <c r="A27" s="28"/>
+      <c r="J27" s="29"/>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="31"/>
-      <c r="J28" s="32"/>
+      <c r="A28" s="28"/>
+      <c r="J28" s="29"/>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="26"/>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="28"/>
+      <c r="A29" s="23"/>
+      <c r="B29" s="24"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="24"/>
+      <c r="H29" s="24"/>
+      <c r="I29" s="24"/>
+      <c r="J29" s="25"/>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="19" t="s">
+      <c r="A30" s="16" t="s">
         <v>12</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="16" t="s">
         <v>12</v>
       </c>
       <c r="D30" s="1" t="s">
@@ -3338,13 +3317,13 @@
       <c r="F30" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H30" s="19" t="s">
+      <c r="H30" s="16" t="s">
         <v>12</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J30" s="19" t="s">
+      <c r="J30" s="16" t="s">
         <v>12</v>
       </c>
     </row>
@@ -3364,10 +3343,10 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="17.25" style="1" customWidth="1"/>
-    <col min="2" max="2" width="41.125" style="19" customWidth="1"/>
-    <col min="3" max="3" width="25.25" style="19" customWidth="1"/>
-    <col min="4" max="4" width="11.5" style="19" customWidth="1"/>
-    <col min="5" max="5" width="47" style="19" customWidth="1"/>
+    <col min="2" max="2" width="41.125" style="16" customWidth="1"/>
+    <col min="3" max="3" width="25.25" style="16" customWidth="1"/>
+    <col min="4" max="4" width="11.5" style="16" customWidth="1"/>
+    <col min="5" max="5" width="47" style="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="23" customHeight="1" spans="1:5">
@@ -3377,13 +3356,13 @@
       <c r="B1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="17" t="s">
         <v>63</v>
       </c>
     </row>
@@ -3391,16 +3370,16 @@
       <c r="A2" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="21" t="s">
+      <c r="B2" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="22">
+      <c r="D2" s="19">
         <v>45.5</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="18" t="s">
         <v>65</v>
       </c>
     </row>
@@ -3408,16 +3387,16 @@
       <c r="A3" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D3" s="22">
+      <c r="D3" s="19">
         <v>20.5</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="18" t="s">
         <v>69</v>
       </c>
     </row>
@@ -3425,16 +3404,16 @@
       <c r="A4" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="19">
         <v>39.8</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="18" t="s">
         <v>73</v>
       </c>
     </row>
@@ -3442,16 +3421,16 @@
       <c r="A5" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B5" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="21" t="s">
+      <c r="B5" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="19">
         <v>45.5</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="18" t="s">
         <v>75</v>
       </c>
     </row>
@@ -3459,50 +3438,50 @@
       <c r="A6" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="19">
         <v>20.5</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="18" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="7" ht="27" customHeight="1" spans="1:5">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="19">
         <v>45.5</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="E7" s="18" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="8" ht="27" customHeight="1" spans="1:5">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="19">
         <v>10.8</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="18" t="s">
         <v>83</v>
       </c>
     </row>
@@ -3510,16 +3489,16 @@
       <c r="A9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="19">
         <v>25</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" s="18" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3527,16 +3506,16 @@
       <c r="A10" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="19">
         <v>23.9</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" s="18" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3544,16 +3523,16 @@
       <c r="A11" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="19">
         <v>22.7</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E11" s="18" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3561,50 +3540,50 @@
       <c r="A12" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="19">
         <v>102.3</v>
       </c>
-      <c r="E12" s="21" t="s">
+      <c r="E12" s="18" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="19">
         <v>20.5</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="E13" s="18" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="19">
         <v>30.7</v>
       </c>
-      <c r="E14" s="21" t="s">
+      <c r="E14" s="18" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3612,50 +3591,50 @@
       <c r="A15" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C15" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="19">
         <v>56.8</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="E15" s="18" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="19">
         <v>28.4</v>
       </c>
-      <c r="E16" s="21" t="s">
+      <c r="E16" s="18" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="19">
         <v>68.2</v>
       </c>
-      <c r="E17" s="21" t="s">
+      <c r="E17" s="18" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3663,16 +3642,16 @@
       <c r="A18" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="19">
         <v>22.7</v>
       </c>
-      <c r="E18" s="21" t="s">
+      <c r="E18" s="18" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3680,16 +3659,16 @@
       <c r="A19" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="C19" s="21" t="s">
+      <c r="C19" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="19">
         <v>56.8</v>
       </c>
-      <c r="E19" s="21" t="s">
+      <c r="E19" s="18" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3697,50 +3676,50 @@
       <c r="A20" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="19">
         <v>90.9</v>
       </c>
-      <c r="E20" s="21" t="s">
+      <c r="E20" s="18" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="B21" s="23" t="s">
+      <c r="B21" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="C21" s="21" t="s">
+      <c r="C21" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="19">
         <v>11.4</v>
       </c>
-      <c r="E21" s="21" t="s">
+      <c r="E21" s="18" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="B22" s="23" t="s">
+      <c r="B22" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="C22" s="21" t="s">
+      <c r="C22" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="19">
         <v>54</v>
       </c>
-      <c r="E22" s="21" t="s">
+      <c r="E22" s="18" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3748,16 +3727,16 @@
       <c r="A23" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B23" s="21" t="s">
+      <c r="B23" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="C23" s="21" t="s">
+      <c r="C23" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="19">
         <v>45.5</v>
       </c>
-      <c r="E23" s="21" t="s">
+      <c r="E23" s="18" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3765,17 +3744,17 @@
       <c r="A24" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="25"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="22"/>
     </row>
     <row r="25" ht="16" customHeight="1" spans="1:5">
-      <c r="A25" s="26"/>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="28"/>
+      <c r="A25" s="23"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3917,25 +3896,25 @@
       <c r="B4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>135</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>136</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>116</v>
       </c>
       <c r="F4" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>137</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>138</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="6">
         <v>45.5</v>
       </c>
       <c r="J4" s="5" t="s">
@@ -3947,25 +3926,25 @@
     </row>
     <row r="5" ht="27" customHeight="1" spans="1:11">
       <c r="A5" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>90</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>143</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>9</v>
@@ -3982,25 +3961,25 @@
     </row>
     <row r="6" ht="27" customHeight="1" spans="1:11">
       <c r="A6" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="C6" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F6" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>146</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>147</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>11</v>
@@ -4017,25 +3996,25 @@
     </row>
     <row r="7" ht="27" customHeight="1" spans="1:11">
       <c r="A7" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="C7" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>116</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>15</v>
@@ -4052,25 +4031,25 @@
     </row>
     <row r="8" ht="27" customHeight="1" spans="1:11">
       <c r="A8" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="C8" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>116</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>152</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>58</v>
@@ -4087,25 +4066,25 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:11">
       <c r="A9" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>157</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>55</v>
@@ -4122,13 +4101,13 @@
     </row>
     <row r="10" ht="40.5" customHeight="1" spans="1:11">
       <c r="A10" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>126</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>13</v>
@@ -4137,10 +4116,10 @@
         <v>8</v>
       </c>
       <c r="F10" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>161</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>58</v>
@@ -4157,25 +4136,25 @@
     </row>
     <row r="11" ht="40.5" customHeight="1" spans="1:11">
       <c r="A11" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>126</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>162</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>163</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F11" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>165</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>34</v>
@@ -4192,25 +4171,25 @@
     </row>
     <row r="12" ht="40.5" customHeight="1" spans="1:11">
       <c r="A12" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="F12" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>15</v>
@@ -4227,10 +4206,10 @@
     </row>
     <row r="13" ht="27" customHeight="1" spans="1:11">
       <c r="A13" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>29</v>
@@ -4242,10 +4221,10 @@
         <v>41</v>
       </c>
       <c r="F13" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>173</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>174</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>52</v>
@@ -4254,7 +4233,7 @@
         <v>11.3636363636364</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>29</v>
@@ -4262,7 +4241,7 @@
     </row>
     <row r="14" ht="27" customHeight="1" spans="1:11">
       <c r="A14" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>126</v>
@@ -4271,16 +4250,16 @@
         <v>29</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>41</v>
       </c>
       <c r="F14" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>178</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>52</v>
@@ -4297,28 +4276,28 @@
     </row>
     <row r="15" ht="67.5" customHeight="1" spans="1:11">
       <c r="A15" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F15" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>182</v>
       </c>
       <c r="I15" s="4">
         <v>11.3636363636364</v>
@@ -4332,25 +4311,25 @@
     </row>
     <row r="16" ht="54" customHeight="1" spans="1:11">
       <c r="A16" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D16" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="F16" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>186</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>9</v>
@@ -4359,7 +4338,7 @@
         <v>77.2727272727273</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>29</v>
@@ -4367,28 +4346,28 @@
     </row>
     <row r="17" ht="54" customHeight="1" spans="1:11">
       <c r="A17" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>187</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>188</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>41</v>
       </c>
       <c r="F17" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>190</v>
-      </c>
       <c r="H17" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I17" s="4">
         <v>18.1818181818182</v>
@@ -4402,25 +4381,25 @@
     </row>
     <row r="18" ht="40.5" customHeight="1" spans="1:11">
       <c r="A18" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F18" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>192</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>193</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>44</v>
@@ -4437,25 +4416,25 @@
     </row>
     <row r="19" ht="27" customHeight="1" spans="1:11">
       <c r="A19" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>116</v>
       </c>
       <c r="F19" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>195</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>196</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>15</v>
@@ -4472,28 +4451,28 @@
     </row>
     <row r="20" ht="54" customHeight="1" spans="1:11">
       <c r="A20" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="F20" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="G20" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>202</v>
       </c>
       <c r="I20" s="4">
         <v>17.0454545454545</v>
@@ -4507,30 +4486,30 @@
     </row>
     <row r="21" ht="67.5" spans="1:11">
       <c r="A21" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="5" t="s">
         <v>29</v>
       </c>
       <c r="F21" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>204</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>205</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="I21" s="7">
+      <c r="I21" s="6">
         <v>23.9</v>
       </c>
       <c r="J21" s="5" t="s">
@@ -4541,61 +4520,61 @@
       </c>
     </row>
     <row r="22" ht="81" spans="1:11">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="C22" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="D22" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="D22" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E22" s="10" t="s">
+      <c r="F22" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="G22" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="H22" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="H22" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="I22" s="11">
+      <c r="I22" s="9">
         <v>39.8</v>
       </c>
-      <c r="J22" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="K22" s="9" t="s">
+      <c r="J22" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K22" s="7" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="23" ht="27" customHeight="1" spans="1:11">
       <c r="A23" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>214</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>215</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F23" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>216</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>217</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>28</v>
@@ -4607,33 +4586,33 @@
         <v>29</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="24" ht="27" customHeight="1" spans="1:11">
       <c r="A24" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>220</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>221</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F24" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>223</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>224</v>
       </c>
       <c r="I24" s="4">
         <v>28.4090909090909</v>
@@ -4647,25 +4626,25 @@
     </row>
     <row r="25" ht="54" customHeight="1" spans="1:11">
       <c r="A25" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="E25" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="F25" s="3" t="s">
+      <c r="G25" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>55</v>
@@ -4682,28 +4661,28 @@
     </row>
     <row r="26" ht="54" customHeight="1" spans="1:11">
       <c r="A26" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>76</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>78</v>
       </c>
       <c r="F26" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="H26" s="3" t="s">
         <v>231</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>232</v>
       </c>
       <c r="I26" s="4">
         <v>20.4545454545455</v>
@@ -4717,10 +4696,10 @@
     </row>
     <row r="27" ht="40.5" customHeight="1" spans="1:11">
       <c r="A27" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>93</v>
@@ -4732,10 +4711,10 @@
         <v>41</v>
       </c>
       <c r="F27" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>233</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>234</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>55</v>
@@ -4752,10 +4731,10 @@
     </row>
     <row r="28" ht="40.5" customHeight="1" spans="1:11">
       <c r="A28" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>95</v>
@@ -4767,13 +4746,13 @@
         <v>39</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G28" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="H28" s="3" t="s">
         <v>235</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>236</v>
       </c>
       <c r="I28" s="4">
         <v>30.6818181818182</v>
@@ -4787,12 +4766,12 @@
     </row>
     <row r="29" ht="54" customHeight="1" spans="1:11">
       <c r="A29" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C29" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="C29" s="10" t="s">
         <v>79</v>
       </c>
       <c r="D29" s="3" t="s">
@@ -4802,13 +4781,13 @@
         <v>8</v>
       </c>
       <c r="F29" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="H29" s="3" t="s">
         <v>238</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>239</v>
       </c>
       <c r="I29" s="4">
         <v>45.4545454545455</v>
@@ -4822,12 +4801,12 @@
     </row>
     <row r="30" ht="54" customHeight="1" spans="1:11">
       <c r="A30" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C30" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="C30" s="10" t="s">
         <v>82</v>
       </c>
       <c r="D30" s="3" t="s">
@@ -4837,10 +4816,10 @@
         <v>10</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H30" s="3">
         <v>1200</v>
@@ -4852,30 +4831,30 @@
         <v>131</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="31" ht="40.5" customHeight="1" spans="1:11">
       <c r="A31" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>242</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>243</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>41</v>
       </c>
       <c r="F31" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="G31" s="3" t="s">
         <v>244</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>245</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>11</v>
@@ -4892,10 +4871,10 @@
     </row>
     <row r="32" ht="40.5" customHeight="1" spans="1:11">
       <c r="A32" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>96</v>
@@ -4907,13 +4886,13 @@
         <v>39</v>
       </c>
       <c r="F32" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="G32" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="H32" s="3" t="s">
         <v>248</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>249</v>
       </c>
       <c r="I32" s="4">
         <v>56.8181818181818</v>
@@ -4927,7 +4906,7 @@
     </row>
     <row r="33" ht="40.5" customHeight="1" spans="1:11">
       <c r="A33" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>29</v>
@@ -4942,13 +4921,13 @@
         <v>41</v>
       </c>
       <c r="F33" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G33" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="G33" s="3" t="s">
+      <c r="H33" s="3" t="s">
         <v>251</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>252</v>
       </c>
       <c r="I33" s="4">
         <v>28.4090909090909</v>
@@ -4962,7 +4941,7 @@
     </row>
     <row r="34" ht="54" customHeight="1" spans="1:11">
       <c r="A34" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>29</v>
@@ -4977,13 +4956,13 @@
         <v>39</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G34" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="H34" s="3" t="s">
         <v>253</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>254</v>
       </c>
       <c r="I34" s="4">
         <v>68.1818181818182</v>
@@ -4997,28 +4976,28 @@
     </row>
     <row r="35" ht="54" customHeight="1" spans="1:11">
       <c r="A35" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="D35" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E35" s="3" t="s">
+      <c r="F35" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="G35" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>259</v>
-      </c>
       <c r="H35" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I35" s="4">
         <v>45.4545454545455</v>
@@ -5032,25 +5011,25 @@
     </row>
     <row r="36" ht="40.5" customHeight="1" spans="1:11">
       <c r="A36" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C36" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>260</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>261</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>50</v>
       </c>
       <c r="F36" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="G36" s="3" t="s">
         <v>262</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>263</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>12</v>
@@ -5067,28 +5046,28 @@
     </row>
     <row r="37" ht="40.5" customHeight="1" spans="1:11">
       <c r="A37" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="D37" s="3" t="s">
         <v>265</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>266</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F37" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G37" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="G37" s="3" t="s">
+      <c r="H37" s="3" t="s">
         <v>268</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>269</v>
       </c>
       <c r="I37" s="4">
         <v>31.8181818181818</v>
@@ -5102,25 +5081,25 @@
     </row>
     <row r="38" ht="81" customHeight="1" spans="1:11">
       <c r="A38" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>270</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>271</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>116</v>
       </c>
       <c r="F38" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="G38" s="3" t="s">
         <v>272</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>273</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>58</v>
@@ -5137,25 +5116,25 @@
     </row>
     <row r="39" ht="54" customHeight="1" spans="1:11">
       <c r="A39" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F39" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="G39" s="3" t="s">
         <v>275</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>276</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>11</v>
@@ -5172,25 +5151,25 @@
     </row>
     <row r="40" ht="54" customHeight="1" spans="1:11">
       <c r="A40" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>116</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>15</v>
@@ -5207,25 +5186,25 @@
     </row>
     <row r="41" ht="40.5" customHeight="1" spans="1:11">
       <c r="A41" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C41" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>279</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>280</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F41" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="G41" s="3" t="s">
         <v>281</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>282</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>11</v>
@@ -5242,25 +5221,25 @@
     </row>
     <row r="42" ht="54" customHeight="1" spans="1:11">
       <c r="A42" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="D42" s="3" t="s">
         <v>284</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>285</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F42" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="G42" s="3" t="s">
         <v>286</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>287</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>9</v>
@@ -5277,25 +5256,25 @@
     </row>
     <row r="43" ht="54" customHeight="1" spans="1:11">
       <c r="A43" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C43" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>288</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>289</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>116</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>58</v>
@@ -5312,25 +5291,25 @@
     </row>
     <row r="44" ht="67.5" customHeight="1" spans="1:11">
       <c r="A44" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C44" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>291</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>292</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F44" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="G44" s="3" t="s">
         <v>293</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>294</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>11</v>
@@ -5347,25 +5326,25 @@
     </row>
     <row r="45" ht="67.5" customHeight="1" spans="1:11">
       <c r="A45" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>116</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>15</v>
@@ -5382,25 +5361,25 @@
     </row>
     <row r="46" ht="67.5" customHeight="1" spans="1:11">
       <c r="A46" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F46" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="G46" s="3" t="s">
         <v>298</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>299</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>52</v>
@@ -5417,13 +5396,13 @@
     </row>
     <row r="47" ht="40.5" customHeight="1" spans="1:11">
       <c r="A47" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>103</v>
@@ -5432,10 +5411,10 @@
         <v>8</v>
       </c>
       <c r="F47" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="G47" s="3" t="s">
         <v>301</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>302</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>58</v>
@@ -5452,13 +5431,13 @@
     </row>
     <row r="48" ht="40.5" customHeight="1" spans="1:11">
       <c r="A48" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>103</v>
@@ -5467,10 +5446,10 @@
         <v>104</v>
       </c>
       <c r="F48" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="G48" s="3" t="s">
         <v>304</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>305</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>44</v>
@@ -5487,25 +5466,25 @@
     </row>
     <row r="49" ht="40.5" spans="1:11">
       <c r="A49" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>116</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>15</v>
@@ -5522,10 +5501,10 @@
     </row>
     <row r="50" ht="40.5" customHeight="1" spans="1:11">
       <c r="A50" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>105</v>
@@ -5537,10 +5516,10 @@
         <v>116</v>
       </c>
       <c r="F50" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="G50" s="3" t="s">
         <v>308</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>309</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>9</v>
@@ -5557,30 +5536,30 @@
     </row>
     <row r="51" ht="45" customHeight="1" spans="1:11">
       <c r="A51" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E51" s="10" t="s">
+      <c r="E51" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="F51" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="F51" s="5" t="s">
-        <v>312</v>
-      </c>
       <c r="G51" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="H51" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="H51" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="I51" s="7">
+      <c r="I51" s="6">
         <v>20.5</v>
       </c>
       <c r="J51" s="5" t="s">
@@ -5592,25 +5571,25 @@
     </row>
     <row r="52" ht="54" customHeight="1" spans="1:11">
       <c r="A52" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>313</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>314</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F52" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="G52" s="3" t="s">
         <v>315</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>316</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>58</v>
@@ -5626,66 +5605,66 @@
       </c>
     </row>
     <row r="53" ht="108" spans="1:11">
-      <c r="A53" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="B53" s="13" t="s">
+      <c r="A53" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="C53" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="C53" s="14" t="s">
+      <c r="D53" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E53" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="D53" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="E53" s="10" t="s">
+      <c r="F53" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="F53" s="13" t="s">
+      <c r="G53" s="11" t="s">
         <v>320</v>
       </c>
-      <c r="G53" s="13" t="s">
+      <c r="H53" s="11" t="s">
         <v>321</v>
       </c>
-      <c r="H53" s="13" t="s">
+      <c r="I53" s="13">
+        <v>45.5</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K53" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="54" ht="81" spans="1:11">
+      <c r="A54" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E54" s="14" t="s">
+        <v>318</v>
+      </c>
+      <c r="F54" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="I53" s="15">
-        <v>45.5</v>
-      </c>
-      <c r="J53" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="K53" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="54" ht="81" spans="1:11">
-      <c r="A54" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C54" s="16" t="s">
+      <c r="G54" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="D54" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E54" s="17" t="s">
-        <v>319</v>
-      </c>
-      <c r="F54" s="5" t="s">
+      <c r="H54" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="G54" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="H54" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="I54" s="7">
+      <c r="I54" s="6">
         <v>45.5</v>
       </c>
       <c r="J54" s="5" t="s">
@@ -5697,25 +5676,25 @@
     </row>
     <row r="55" ht="40.5" customHeight="1" spans="1:11">
       <c r="A55" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C55" s="3" t="s">
+      <c r="E55" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="F55" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="E55" s="3" t="s">
+      <c r="G55" s="3" t="s">
         <v>330</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>332</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>9</v>
@@ -5732,25 +5711,25 @@
     </row>
     <row r="56" ht="40.5" customHeight="1" spans="1:11">
       <c r="A56" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="D56" s="3" t="s">
         <v>327</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>329</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>104</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>9</v>
@@ -5759,36 +5738,36 @@
         <v>20.4545454545455</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="K56" s="18">
+        <v>332</v>
+      </c>
+      <c r="K56" s="15">
         <v>0.88</v>
       </c>
     </row>
     <row r="57" ht="27" customHeight="1" spans="1:11">
       <c r="A57" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="D57" s="3" t="s">
         <v>336</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>338</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F57" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="H57" s="3" t="s">
         <v>339</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>341</v>
       </c>
       <c r="I57" s="4">
         <v>18.1818181818182</v>
@@ -5802,7 +5781,7 @@
     </row>
     <row r="58" ht="40.5" customHeight="1" spans="1:11">
       <c r="A58" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>126</v>
@@ -5811,16 +5790,16 @@
         <v>108</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>9</v>
@@ -5837,25 +5816,25 @@
     </row>
     <row r="59" ht="67.5" customHeight="1" spans="1:11">
       <c r="A59" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C59" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="F59" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="G59" s="3" t="s">
         <v>346</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>348</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>15</v>
@@ -5872,25 +5851,25 @@
     </row>
     <row r="60" ht="40.5" customHeight="1" spans="1:11">
       <c r="A60" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C60" s="3" t="s">
-        <v>349</v>
+      <c r="C60" s="10" t="s">
+        <v>111</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>11</v>
@@ -5899,7 +5878,7 @@
         <v>11.3636363636364</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>29</v>
@@ -5907,25 +5886,25 @@
     </row>
     <row r="61" ht="40.5" customHeight="1" spans="1:11">
       <c r="A61" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C61" s="3" t="s">
-        <v>353</v>
+      <c r="C61" s="10" t="s">
+        <v>113</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>28</v>
@@ -5934,7 +5913,7 @@
         <v>53.9772727272727</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K61" s="3" t="s">
         <v>29</v>
@@ -5942,28 +5921,28 @@
     </row>
     <row r="62" ht="27" customHeight="1" spans="1:11">
       <c r="A62" s="3" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>104</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="I62" s="4">
         <v>56.8181818181818</v>
@@ -5972,30 +5951,30 @@
         <v>131</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="63" ht="27" customHeight="1" spans="1:11">
       <c r="A63" s="3" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C63" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="G63" s="3" t="s">
         <v>361</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>365</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>15</v>
@@ -6012,7 +5991,7 @@
     </row>
     <row r="64" ht="40.5" customHeight="1" spans="1:11">
       <c r="A64" s="3" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>29</v>
@@ -6021,16 +6000,16 @@
         <v>29</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>11</v>
@@ -6047,28 +6026,28 @@
     </row>
     <row r="65" ht="54" customHeight="1" spans="1:11">
       <c r="A65" s="3" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I65" s="4">
         <v>29.5454545454545</v>
@@ -6082,25 +6061,25 @@
     </row>
     <row r="66" ht="40.5" customHeight="1" spans="1:11">
       <c r="A66" s="3" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>116</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>58</v>
@@ -6117,25 +6096,25 @@
     </row>
     <row r="67" ht="27" customHeight="1" spans="1:11">
       <c r="A67" s="3" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>11</v>
@@ -6152,7 +6131,7 @@
     </row>
     <row r="68" ht="67.5" customHeight="1" spans="1:11">
       <c r="A68" s="3" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>126</v>
@@ -6161,16 +6140,16 @@
         <v>29</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>14</v>
@@ -6179,7 +6158,7 @@
         <v>5.68181818181818</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="K68" s="3" t="s">
         <v>29</v>
@@ -6187,7 +6166,7 @@
     </row>
     <row r="69" ht="67.5" customHeight="1" spans="1:11">
       <c r="A69" s="3" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>126</v>
@@ -6196,16 +6175,16 @@
         <v>29</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>14</v>
@@ -6222,28 +6201,28 @@
     </row>
     <row r="70" ht="40.5" customHeight="1" spans="1:11">
       <c r="A70" s="3" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>126</v>
       </c>
       <c r="C70" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="H70" s="3" t="s">
         <v>392</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>396</v>
       </c>
       <c r="I70" s="4">
         <v>12.5</v>
@@ -6257,13 +6236,13 @@
     </row>
     <row r="71" ht="43" customHeight="1" spans="1:11">
       <c r="A71" s="3" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>29</v>
@@ -6272,10 +6251,10 @@
         <v>8</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>58</v>
@@ -6292,25 +6271,25 @@
     </row>
     <row r="72" ht="81" customHeight="1" spans="1:11">
       <c r="A72" s="3" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B72" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D72" s="3" t="s">
         <v>398</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>402</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>58</v>
@@ -6327,25 +6306,25 @@
     </row>
     <row r="73" ht="35" customHeight="1" spans="1:11">
       <c r="A73" s="3" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>116</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>28</v>
@@ -6354,7 +6333,7 @@
         <v>12.5</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K73" s="3" t="s">
         <v>29</v>
@@ -6362,34 +6341,34 @@
     </row>
     <row r="74" ht="40.5" customHeight="1" spans="1:11">
       <c r="A74" s="3" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B74" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="G74" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="C74" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D74" s="3" t="s">
+      <c r="H74" s="3" t="s">
         <v>411</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>415</v>
       </c>
       <c r="I74" s="4">
         <v>9.09090909090909</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K74" s="3" t="s">
         <v>29</v>
@@ -6397,28 +6376,28 @@
     </row>
     <row r="75" ht="67.5" customHeight="1" spans="1:11">
       <c r="A75" s="3" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B75" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="H75" s="3" t="s">
         <v>416</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>420</v>
       </c>
       <c r="I75" s="4">
         <v>17.0454545454545</v>
